--- a/jira_export_2026-10-08.xlsx
+++ b/jira_export_2026-10-08.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2,445 €</t>
+          <t>3,355 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>1,718 €</t>
+          <t>2,628 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>109 h</t>
+          <t>122 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P132"/>
+  <dimension ref="A1:P137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1525,7 +1525,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L16" s="15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>2</v>
       </c>
       <c r="K20" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20" s="15" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>4</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
@@ -3973,10 +3973,10 @@
         <v>2696</v>
       </c>
       <c r="O45" s="13" t="n">
-        <v>0</v>
+        <v>909.9</v>
       </c>
       <c r="P45" s="12" t="n">
-        <v>0</v>
+        <v>303.3</v>
       </c>
     </row>
     <row r="46">
@@ -4101,7 +4101,7 @@
         <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>6</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
@@ -7502,27 +7502,27 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-29964</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>SAINT DIZIER</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -7549,22 +7549,22 @@
         <v>9</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>3.25</v>
+        <v>0.5</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-29965</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00152739</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>204.14</v>
-      </c>
-      <c r="O95" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="12" t="n">
@@ -7574,26 +7574,28 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E96" s="15" t="n">
-        <v/>
+          <t>MAIRE DE PONTARLIER</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
+        </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
@@ -7612,29 +7614,29 @@
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0.5</v>
+        <v>3.25</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="16" t="n">
+        <v>204.14</v>
+      </c>
+      <c r="O96" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="16" t="n">
@@ -7644,12 +7646,12 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7659,7 +7661,7 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
+          <t>COMMUNE DE CARCASSONNE</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -7677,34 +7679,34 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>401.54</v>
-      </c>
-      <c r="O97" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="12" t="n">
@@ -7714,12 +7716,12 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
@@ -7729,13 +7731,11 @@
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E98" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v/>
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
@@ -7754,27 +7754,27 @@
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>275</v>
+        <v>401.54</v>
       </c>
       <c r="O98" s="13" t="n">
         <v>0</v>
@@ -7833,22 +7833,22 @@
         <v>11</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="12" t="n">
+        <v>275</v>
+      </c>
+      <c r="O99" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
@@ -7905,22 +7905,22 @@
         <v>11</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>1790</v>
-      </c>
-      <c r="O100" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="16" t="n">
@@ -7977,22 +7977,22 @@
         <v>11</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="12" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O101" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="12" t="n">
@@ -8049,16 +8049,16 @@
         <v>11</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
@@ -8074,12 +8074,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8089,11 +8089,13 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E103" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
         <is>
@@ -8112,29 +8114,29 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O103" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="12" t="n">
@@ -8144,12 +8146,12 @@
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
@@ -8159,7 +8161,7 @@
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E104" s="15" t="n">
@@ -8177,12 +8179,12 @@
       </c>
       <c r="H104" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
@@ -8193,16 +8195,16 @@
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="O104" s="13" t="n">
         <v>0</v>
@@ -8214,22 +8216,22 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8252,44 +8254,44 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>3016.08</v>
+        <v>460</v>
       </c>
       <c r="O105" s="13" t="n">
-        <v>418.9</v>
+        <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
-        <v>69.81999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
@@ -8299,7 +8301,7 @@
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E106" s="15" t="n">
@@ -8322,54 +8324,54 @@
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>0.25</v>
+        <v>6</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
-        <v>1200</v>
+        <v>3016.08</v>
       </c>
       <c r="O106" s="13" t="n">
-        <v>0</v>
+        <v>418.9</v>
       </c>
       <c r="P106" s="16" t="n">
-        <v>0</v>
+        <v>69.81999999999999</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8387,32 +8389,32 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>3919.06</v>
+        <v>1200</v>
       </c>
       <c r="O107" s="13" t="n">
         <v>0</v>
@@ -8424,12 +8426,12 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
@@ -8439,7 +8441,7 @@
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E108" s="15" t="n">
@@ -8462,29 +8464,29 @@
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="16" t="n">
+        <v>3919.06</v>
+      </c>
+      <c r="O108" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="16" t="n">
@@ -8494,12 +8496,12 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -8509,7 +8511,7 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8532,23 +8534,23 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
         <v>15</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>0.19</v>
+        <v>0.5</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
@@ -8609,16 +8611,16 @@
         <v>15</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
@@ -8649,7 +8651,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8679,16 +8681,16 @@
         <v>15</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
@@ -8719,7 +8721,7 @@
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E112" s="15" t="n">
@@ -8749,16 +8751,16 @@
         <v>15</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
@@ -8774,12 +8776,12 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
@@ -8789,7 +8791,7 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8807,34 +8809,34 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="O113" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="12" t="n">
@@ -8844,22 +8846,22 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8882,27 +8884,27 @@
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
         <v>18</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="O114" s="13" t="n">
         <v>0</v>
@@ -8914,12 +8916,12 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
@@ -8929,7 +8931,7 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8947,34 +8949,34 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O115" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="12" t="n">
@@ -8984,12 +8986,12 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
@@ -8999,7 +9001,7 @@
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E116" s="15" t="n">
@@ -9022,23 +9024,23 @@
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
@@ -9054,12 +9056,12 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -9069,13 +9071,11 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v/>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
@@ -9084,27 +9084,35 @@
       </c>
       <c r="G117" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K117" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L117" s="11" t="inlineStr"/>
-      <c r="M117" s="11" t="inlineStr"/>
+      <c r="L117" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M117" s="11" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N117" s="12" t="n">
         <v>0</v>
       </c>
@@ -9118,12 +9126,12 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
@@ -9133,11 +9141,13 @@
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
@@ -9151,19 +9161,19 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L118" s="15" t="inlineStr"/>
       <c r="M118" s="15" t="inlineStr"/>
@@ -9180,22 +9190,22 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9203,44 +9213,36 @@
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
         <v>22</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M119" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L119" s="11" t="inlineStr"/>
+      <c r="M119" s="11" t="inlineStr"/>
       <c r="N119" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O119" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="12" t="n">
@@ -9250,22 +9252,22 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -9273,7 +9275,7 @@
       </c>
       <c r="F120" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G120" s="15" t="inlineStr">
@@ -9283,12 +9285,12 @@
       </c>
       <c r="H120" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
@@ -9299,16 +9301,16 @@
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O120" s="13" t="n">
         <v>0</v>
@@ -9320,22 +9322,22 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9348,7 +9350,7 @@
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
@@ -9358,21 +9360,29 @@
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L121" s="11" t="inlineStr"/>
-      <c r="M121" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L121" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M121" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N121" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O121" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="12" t="n">
@@ -9382,22 +9392,22 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
@@ -9420,14 +9430,14 @@
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="L122" s="15" t="inlineStr"/>
       <c r="M122" s="15" t="inlineStr"/>
@@ -9444,12 +9454,12 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
@@ -9459,7 +9469,7 @@
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9477,19 +9487,19 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L123" s="11" t="inlineStr"/>
       <c r="M123" s="11" t="inlineStr"/>
@@ -9506,22 +9516,22 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9537,17 +9547,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H124" s="15" t="inlineStr"/>
+      <c r="H124" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L124" s="15" t="inlineStr"/>
       <c r="M124" s="15" t="inlineStr"/>
@@ -9564,12 +9578,12 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
@@ -9579,7 +9593,7 @@
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9595,32 +9609,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H125" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H125" s="11" t="inlineStr"/>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L125" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M125" s="11" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L125" s="11" t="inlineStr"/>
+      <c r="M125" s="11" t="inlineStr"/>
       <c r="N125" s="12" t="n">
         <v>0</v>
       </c>
@@ -9634,22 +9636,22 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9662,29 +9664,33 @@
       </c>
       <c r="G126" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H126" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H126" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
         <v>37</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>0.75</v>
+        <v>5</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N126" s="16" t="n">
@@ -9700,24 +9706,26 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C127" s="11" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E127" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="n">
+        <v/>
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
@@ -9726,27 +9734,31 @@
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H127" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H127" s="11" t="inlineStr"/>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L127" s="11" t="inlineStr"/>
-      <c r="M127" s="11" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="L127" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N127" s="12" t="n">
         <v>0</v>
       </c>
@@ -9760,21 +9772,25 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr"/>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E128" s="15" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E128" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F128" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9782,35 +9798,31 @@
       </c>
       <c r="G128" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H128" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H128" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M128" s="15" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L128" s="15" t="inlineStr"/>
+      <c r="M128" s="15" t="inlineStr"/>
       <c r="N128" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="O128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="16" t="n">
@@ -9820,18 +9832,18 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr"/>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr"/>
@@ -9848,14 +9860,14 @@
       <c r="H129" s="11" t="inlineStr"/>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="L129" s="11" t="inlineStr"/>
       <c r="M129" s="11" t="inlineStr"/>
@@ -9872,18 +9884,18 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr"/>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="E130" s="15" t="inlineStr"/>
@@ -9894,31 +9906,23 @@
       </c>
       <c r="G130" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H130" s="15" t="inlineStr"/>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L130" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M130" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L130" s="15" t="inlineStr"/>
+      <c r="M130" s="15" t="inlineStr"/>
       <c r="N130" s="16" t="n">
         <v>0</v>
       </c>
@@ -9932,18 +9936,18 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr"/>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr"/>
@@ -9954,67 +9958,343 @@
       </c>
       <c r="G131" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr"/>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K131" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L131" s="11" t="inlineStr">
+      <c r="L131" s="11" t="inlineStr"/>
+      <c r="M131" s="11" t="inlineStr"/>
+      <c r="N131" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1339</t>
+        </is>
+      </c>
+      <c r="B132" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
+        </is>
+      </c>
+      <c r="C132" s="15" t="inlineStr"/>
+      <c r="D132" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
+        </is>
+      </c>
+      <c r="E132" s="15" t="inlineStr"/>
+      <c r="F132" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G132" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H132" s="15" t="inlineStr"/>
+      <c r="I132" s="15" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J132" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M132" s="15" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
+      <c r="N132" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="O132" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1320</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>Commune de ETEL</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr"/>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>Commune de ETEL</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr"/>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H133" s="11" t="inlineStr"/>
+      <c r="I133" s="11" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="J133" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K133" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L133" s="11" t="inlineStr"/>
+      <c r="M133" s="11" t="inlineStr"/>
+      <c r="N133" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1288</t>
+        </is>
+      </c>
+      <c r="B134" s="15" t="inlineStr">
+        <is>
+          <t>Mairie d'Aubignan</t>
+        </is>
+      </c>
+      <c r="C134" s="15" t="inlineStr"/>
+      <c r="D134" s="15" t="inlineStr">
+        <is>
+          <t>Mairie d'Aubignan</t>
+        </is>
+      </c>
+      <c r="E134" s="15" t="inlineStr"/>
+      <c r="F134" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G134" s="15" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H134" s="15" t="inlineStr"/>
+      <c r="I134" s="15" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="J134" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K134" s="15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L134" s="15" t="inlineStr"/>
+      <c r="M134" s="15" t="inlineStr"/>
+      <c r="N134" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr"/>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr"/>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G135" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H135" s="11" t="inlineStr"/>
+      <c r="I135" s="11" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J135" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K135" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L135" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M135" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N135" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1047</t>
+        </is>
+      </c>
+      <c r="B136" s="15" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C136" s="15" t="inlineStr"/>
+      <c r="D136" s="15" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E136" s="15" t="inlineStr"/>
+      <c r="F136" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G136" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H136" s="15" t="inlineStr"/>
+      <c r="I136" s="15" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="J136" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="K136" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L136" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-26768</t>
         </is>
       </c>
-      <c r="M131" s="11" t="inlineStr">
+      <c r="M136" s="15" t="inlineStr">
         <is>
           <t>00141775</t>
         </is>
       </c>
-      <c r="N131" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="17" t="inlineStr">
+      <c r="N136" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B132" s="17" t="inlineStr"/>
-      <c r="C132" s="17" t="inlineStr"/>
-      <c r="D132" s="17" t="inlineStr"/>
-      <c r="E132" s="17" t="inlineStr"/>
-      <c r="F132" s="17" t="inlineStr"/>
-      <c r="G132" s="17" t="inlineStr"/>
-      <c r="H132" s="17" t="inlineStr"/>
-      <c r="I132" s="17" t="inlineStr"/>
-      <c r="J132" s="17" t="inlineStr"/>
-      <c r="K132" s="17" t="inlineStr"/>
-      <c r="L132" s="17" t="inlineStr"/>
-      <c r="M132" s="17" t="inlineStr"/>
-      <c r="N132" s="18" t="n">
+      <c r="B137" s="17" t="inlineStr"/>
+      <c r="C137" s="17" t="inlineStr"/>
+      <c r="D137" s="17" t="inlineStr"/>
+      <c r="E137" s="17" t="inlineStr"/>
+      <c r="F137" s="17" t="inlineStr"/>
+      <c r="G137" s="17" t="inlineStr"/>
+      <c r="H137" s="17" t="inlineStr"/>
+      <c r="I137" s="17" t="inlineStr"/>
+      <c r="J137" s="17" t="inlineStr"/>
+      <c r="K137" s="17" t="inlineStr"/>
+      <c r="L137" s="17" t="inlineStr"/>
+      <c r="M137" s="17" t="inlineStr"/>
+      <c r="N137" s="18" t="n">
         <v>122424.762</v>
       </c>
-      <c r="O132" s="18" t="n">
-        <v>2445.3</v>
-      </c>
-      <c r="P132" s="18" t="n">
-        <v>35.14</v>
+      <c r="O137" s="18" t="n">
+        <v>3355.2</v>
+      </c>
+      <c r="P137" s="18" t="n">
+        <v>41.38</v>
       </c>
     </row>
   </sheetData>
@@ -10147,6 +10427,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId132"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10958,16 +11243,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>45</v>
+        <v>49.25</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>10.5</v>
+        <v>10.75</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>1.08</v>
+        <v>2.08</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>56.58</v>
+        <v>62.08</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>7.75</v>
@@ -10977,7 +11262,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
     </row>
@@ -10988,7 +11273,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -10997,7 +11282,7 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -11007,7 +11292,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.1%</t>
         </is>
       </c>
     </row>
@@ -11019,7 +11304,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>30.08</v>
+        <v>32.08</v>
       </c>
     </row>
   </sheetData>
@@ -11104,10 +11389,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>507682</v>
+        <v>506772</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>213769</v>
+        <v>212859</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>293913</v>
@@ -11154,10 +11439,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>242402</v>
+        <v>241492</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>144707</v>
+        <v>143798</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>97694</v>

--- a/jira_export_2026-10-08.xlsx
+++ b/jira_export_2026-10-08.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>122 h</t>
+          <t>123 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>2696</v>
+        <v>1786.1</v>
       </c>
       <c r="O45" s="13" t="n">
         <v>909.9</v>
@@ -6397,7 +6397,7 @@
         <v>7</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
@@ -10288,13 +10288,13 @@
       <c r="L137" s="17" t="inlineStr"/>
       <c r="M137" s="17" t="inlineStr"/>
       <c r="N137" s="18" t="n">
-        <v>122424.762</v>
+        <v>121514.862</v>
       </c>
       <c r="O137" s="18" t="n">
         <v>3355.2</v>
       </c>
       <c r="P137" s="18" t="n">
-        <v>41.38</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -11243,7 +11243,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>49.25</v>
+        <v>50</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>10.75</v>
@@ -11252,7 +11252,7 @@
         <v>2.08</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>62.08</v>
+        <v>62.83</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>7.75</v>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
     </row>
@@ -11392,13 +11392,13 @@
         <v>506772</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>212859</v>
+        <v>216909</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>293913</v>
+        <v>289863</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>227001</v>
+        <v>222951</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>21551</v>
@@ -11442,13 +11442,13 @@
         <v>241492</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>143798</v>
+        <v>147848</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>97694</v>
+        <v>93644</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>50106</v>
+        <v>46056</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>12376</v>

--- a/jira_export_2026-10-08.xlsx
+++ b/jira_export_2026-10-08.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>123 h</t>
+          <t>135 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P137"/>
+  <dimension ref="A1:P138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L6" s="15" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>4</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>3.75</v>
+        <v>6.25</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>7</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
@@ -9190,22 +9190,22 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
@@ -9235,7 +9235,7 @@
         <v>22</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L119" s="11" t="inlineStr"/>
       <c r="M119" s="11" t="inlineStr"/>
@@ -9252,22 +9252,22 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -9275,44 +9275,36 @@
       </c>
       <c r="F120" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G120" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H120" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
         <v>22</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M120" s="15" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L120" s="15" t="inlineStr"/>
+      <c r="M120" s="15" t="inlineStr"/>
       <c r="N120" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O120" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="16" t="n">
@@ -9322,22 +9314,22 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9345,7 +9337,7 @@
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G121" s="11" t="inlineStr">
@@ -9355,12 +9347,12 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
@@ -9371,16 +9363,16 @@
       </c>
       <c r="L121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M121" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N121" s="12" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O121" s="13" t="n">
         <v>0</v>
@@ -9392,22 +9384,22 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
@@ -9420,7 +9412,7 @@
       </c>
       <c r="G122" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H122" s="15" t="inlineStr">
@@ -9430,21 +9422,29 @@
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L122" s="15" t="inlineStr"/>
-      <c r="M122" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L122" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M122" s="15" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N122" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" s="16" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O122" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P122" s="16" t="n">
@@ -9454,22 +9454,22 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9492,14 +9492,14 @@
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="L123" s="11" t="inlineStr"/>
       <c r="M123" s="11" t="inlineStr"/>
@@ -9516,12 +9516,12 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9549,19 +9549,19 @@
       </c>
       <c r="H124" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
         <v>35</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L124" s="15" t="inlineStr"/>
       <c r="M124" s="15" t="inlineStr"/>
@@ -9578,22 +9578,22 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9609,17 +9609,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H125" s="11" t="inlineStr"/>
+      <c r="H125" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L125" s="11" t="inlineStr"/>
       <c r="M125" s="11" t="inlineStr"/>
@@ -9636,12 +9640,12 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
@@ -9651,7 +9655,7 @@
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9667,32 +9671,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H126" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H126" s="15" t="inlineStr"/>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
         <v>37</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="L126" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M126" s="15" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L126" s="15" t="inlineStr"/>
+      <c r="M126" s="15" t="inlineStr"/>
       <c r="N126" s="16" t="n">
         <v>0</v>
       </c>
@@ -9706,22 +9698,22 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9734,29 +9726,33 @@
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H127" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H127" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0.75</v>
+        <v>5.75</v>
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N127" s="12" t="n">
@@ -9772,24 +9768,26 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C128" s="15" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C128" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E128" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v/>
       </c>
       <c r="F128" s="15" t="inlineStr">
         <is>
@@ -9798,17 +9796,13 @@
       </c>
       <c r="G128" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H128" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H128" s="15" t="inlineStr"/>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
@@ -9817,8 +9811,16 @@
       <c r="K128" s="15" t="n">
         <v>0.75</v>
       </c>
-      <c r="L128" s="15" t="inlineStr"/>
-      <c r="M128" s="15" t="inlineStr"/>
+      <c r="L128" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M128" s="15" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N128" s="16" t="n">
         <v>0</v>
       </c>
@@ -9832,21 +9834,25 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr"/>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
-        </is>
-      </c>
-      <c r="E129" s="11" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9854,20 +9860,24 @@
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H129" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H129" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L129" s="11" t="inlineStr"/>
       <c r="M129" s="11" t="inlineStr"/>
@@ -9884,18 +9894,18 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr"/>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="E130" s="15" t="inlineStr"/>
@@ -9912,11 +9922,11 @@
       <c r="H130" s="15" t="inlineStr"/>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K130" s="15" t="n">
         <v>0.25</v>
@@ -9936,18 +9946,18 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr"/>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr"/>
@@ -9964,7 +9974,7 @@
       <c r="H131" s="11" t="inlineStr"/>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
@@ -9988,18 +9998,18 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr"/>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="E132" s="15" t="inlineStr"/>
@@ -10010,35 +10020,27 @@
       </c>
       <c r="G132" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H132" s="15" t="inlineStr"/>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M132" s="15" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L132" s="15" t="inlineStr"/>
+      <c r="M132" s="15" t="inlineStr"/>
       <c r="N132" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="O132" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P132" s="16" t="n">
@@ -10048,18 +10050,18 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr"/>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr"/>
@@ -10070,27 +10072,35 @@
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr"/>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L133" s="11" t="inlineStr"/>
-      <c r="M133" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L133" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M133" s="11" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N133" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="O133" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="12" t="n">
@@ -10100,18 +10110,18 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr"/>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E134" s="15" t="inlineStr"/>
@@ -10128,14 +10138,14 @@
       <c r="H134" s="15" t="inlineStr"/>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="L134" s="15" t="inlineStr"/>
       <c r="M134" s="15" t="inlineStr"/>
@@ -10152,18 +10162,18 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr"/>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr"/>
@@ -10174,31 +10184,23 @@
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr"/>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L135" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M135" s="11" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="L135" s="11" t="inlineStr"/>
+      <c r="M135" s="11" t="inlineStr"/>
       <c r="N135" s="12" t="n">
         <v>0</v>
       </c>
@@ -10212,18 +10214,18 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr"/>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E136" s="15" t="inlineStr"/>
@@ -10240,61 +10242,121 @@
       <c r="H136" s="15" t="inlineStr"/>
       <c r="I136" s="15" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J136" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K136" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L136" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M136" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N136" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1047</t>
+        </is>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr"/>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr"/>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H137" s="11" t="inlineStr"/>
+      <c r="I137" s="11" t="inlineStr">
+        <is>
           <t>04/11/2025</t>
         </is>
       </c>
-      <c r="J136" s="15" t="n">
+      <c r="J137" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="K136" s="15" t="n">
+      <c r="K137" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L136" s="15" t="inlineStr">
+      <c r="L137" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-26768</t>
         </is>
       </c>
-      <c r="M136" s="15" t="inlineStr">
+      <c r="M137" s="11" t="inlineStr">
         <is>
           <t>00141775</t>
         </is>
       </c>
-      <c r="N136" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="17" t="inlineStr">
+      <c r="N137" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B137" s="17" t="inlineStr"/>
-      <c r="C137" s="17" t="inlineStr"/>
-      <c r="D137" s="17" t="inlineStr"/>
-      <c r="E137" s="17" t="inlineStr"/>
-      <c r="F137" s="17" t="inlineStr"/>
-      <c r="G137" s="17" t="inlineStr"/>
-      <c r="H137" s="17" t="inlineStr"/>
-      <c r="I137" s="17" t="inlineStr"/>
-      <c r="J137" s="17" t="inlineStr"/>
-      <c r="K137" s="17" t="inlineStr"/>
-      <c r="L137" s="17" t="inlineStr"/>
-      <c r="M137" s="17" t="inlineStr"/>
-      <c r="N137" s="18" t="n">
+      <c r="B138" s="17" t="inlineStr"/>
+      <c r="C138" s="17" t="inlineStr"/>
+      <c r="D138" s="17" t="inlineStr"/>
+      <c r="E138" s="17" t="inlineStr"/>
+      <c r="F138" s="17" t="inlineStr"/>
+      <c r="G138" s="17" t="inlineStr"/>
+      <c r="H138" s="17" t="inlineStr"/>
+      <c r="I138" s="17" t="inlineStr"/>
+      <c r="J138" s="17" t="inlineStr"/>
+      <c r="K138" s="17" t="inlineStr"/>
+      <c r="L138" s="17" t="inlineStr"/>
+      <c r="M138" s="17" t="inlineStr"/>
+      <c r="N138" s="18" t="n">
         <v>121514.862</v>
       </c>
-      <c r="O137" s="18" t="n">
+      <c r="O138" s="18" t="n">
         <v>3355.2</v>
       </c>
-      <c r="P137" s="18" t="n">
-        <v>41</v>
+      <c r="P138" s="18" t="n">
+        <v>37.25</v>
       </c>
     </row>
   </sheetData>
@@ -10432,6 +10494,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11243,16 +11306,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>50</v>
+        <v>56.75</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>10.75</v>
+        <v>11.75</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>2.08</v>
+        <v>2.58</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>62.83</v>
+        <v>71.08</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>7.75</v>
@@ -11262,7 +11325,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11367,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>32.08</v>
+        <v>36.08</v>
       </c>
     </row>
   </sheetData>
